--- a/nr-update-valueset/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
+++ b/nr-update-valueset/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T16:49:12+00:00</t>
+    <t>2024-03-07T12:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-valueset/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
+++ b/nr-update-valueset/ig/ValueSet-VS-TRE-R74-ModeFixationTarifaire.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>VS_TRE_R74-ModeFixationTarifaire</t>
+    <t>VS_TRE_R74_ModeFixationTarifaire</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T12:17:43+00:00</t>
+    <t>2024-03-07T12:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
